--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SA REAL INSTALACIONES AREVALO IBIZA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SA REAL INSTALACIONES AREVALO IBIZA.xlsx
@@ -565,13 +565,13 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>87.95050000000001</v>
+        <v>76.0014</v>
       </c>
       <c r="E2" t="n">
-        <v>77.96899999999999</v>
+        <v>72.9637</v>
       </c>
       <c r="F2" t="n">
-        <v>9.981300000000001</v>
+        <v>3.0376</v>
       </c>
       <c r="G2" t="n">
         <v>39.9927</v>
@@ -610,13 +610,13 @@
         <v>30.3525</v>
       </c>
       <c r="S2" t="n">
-        <v>17.3105</v>
+        <v>5.3614</v>
       </c>
       <c r="T2" t="n">
-        <v>6.1065</v>
+        <v>1.1013</v>
       </c>
       <c r="U2" t="n">
-        <v>11.204</v>
+        <v>4.2599</v>
       </c>
       <c r="V2" t="n">
         <v>29.6556</v>
@@ -643,13 +643,13 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>12.2975</v>
+        <v>14.4596</v>
       </c>
       <c r="E3" t="n">
-        <v>31.3954</v>
+        <v>31.0383</v>
       </c>
       <c r="F3" t="n">
-        <v>-19.0982</v>
+        <v>-16.5791</v>
       </c>
       <c r="G3" t="n">
         <v>24.57</v>
@@ -688,13 +688,13 @@
         <v>29.1626</v>
       </c>
       <c r="S3" t="n">
-        <v>-7.060899999999999</v>
+        <v>-4.8986</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.364</v>
+        <v>-1.7211</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.696899999999999</v>
+        <v>-3.1778</v>
       </c>
       <c r="V3" t="n">
         <v>0.5412999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MEDORI MORALES</t>
+          <t>J. ROSA DE SOU DA SIL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8.579199999999998</v>
+        <v>4.9285</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8264</v>
+        <v>1.3831</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7528999999999999</v>
+        <v>3.5455</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.753</v>
+        <v>7.1932</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.153</v>
+        <v>-0.9049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3999999999999997</v>
+        <v>8.0982</v>
       </c>
       <c r="J4" t="n">
-        <v>14.0842</v>
+        <v>12.9667</v>
       </c>
       <c r="K4" t="n">
-        <v>8.638399999999999</v>
+        <v>3.9623</v>
       </c>
       <c r="L4" t="n">
-        <v>5.4453</v>
+        <v>9.0046</v>
       </c>
       <c r="M4" t="n">
-        <v>-15.8372</v>
+        <v>-5.7736</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.7916</v>
+        <v>-4.8673</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.045500000000001</v>
+        <v>-0.9063</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9838</v>
+        <v>-1.587</v>
       </c>
       <c r="Q4" t="n">
-        <v>-16.2675</v>
+        <v>-10.5143</v>
       </c>
       <c r="R4" t="n">
-        <v>14.2837</v>
+        <v>8.927299999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>6.4757</v>
+        <v>-2.0265</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0561</v>
+        <v>-2.2044</v>
       </c>
       <c r="U4" t="n">
-        <v>3.419700000000001</v>
+        <v>0.1778999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>5.840400000000001</v>
+        <v>1.349</v>
       </c>
       <c r="W4" t="n">
-        <v>6.9536</v>
+        <v>1.1352</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1133</v>
+        <v>0.2138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOU DA SIL</t>
+          <t>J. MEDORI MORALES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7404000000000005</v>
+        <v>3.7146</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9464999999999999</v>
+        <v>4.8108</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6869</v>
+        <v>-1.0961</v>
       </c>
       <c r="G5" t="n">
-        <v>7.1932</v>
+        <v>-1.753</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9049999999999999</v>
+        <v>-2.153</v>
       </c>
       <c r="I5" t="n">
-        <v>8.0982</v>
+        <v>0.3999999999999997</v>
       </c>
       <c r="J5" t="n">
-        <v>12.9667</v>
+        <v>14.0842</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9623</v>
+        <v>8.638399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>9.0046</v>
+        <v>5.4453</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.7736</v>
+        <v>-15.8372</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.8673</v>
+        <v>-10.7916</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9063</v>
+        <v>-5.045500000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.587</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.5143</v>
+        <v>-16.2675</v>
       </c>
       <c r="R5" t="n">
-        <v>8.927299999999999</v>
+        <v>14.2837</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.2146</v>
+        <v>1.6112</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.5341</v>
+        <v>0.04060000000000008</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.6806</v>
+        <v>1.5707</v>
       </c>
       <c r="V5" t="n">
-        <v>1.349</v>
+        <v>5.840400000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1352</v>
+        <v>6.9536</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2138</v>
+        <v>-1.1133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>L. MALARY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3864</v>
+        <v>0.7298999999999993</v>
       </c>
       <c r="E6" t="n">
-        <v>3.272</v>
+        <v>24.2249</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.885500000000001</v>
+        <v>-23.4953</v>
       </c>
       <c r="G6" t="n">
-        <v>-13.6591</v>
+        <v>10.1714</v>
       </c>
       <c r="H6" t="n">
-        <v>-12.3269</v>
+        <v>9.264100000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3318</v>
+        <v>0.9074</v>
       </c>
       <c r="J6" t="n">
-        <v>4.672800000000001</v>
+        <v>36.945</v>
       </c>
       <c r="K6" t="n">
-        <v>1.899</v>
+        <v>27.3719</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7737</v>
+        <v>9.5732</v>
       </c>
       <c r="M6" t="n">
-        <v>-18.332</v>
+        <v>-26.7736</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.2261</v>
+        <v>-18.1077</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.105799999999999</v>
+        <v>-8.666</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3967000000000001</v>
+        <v>1.5871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.0286</v>
+        <v>-21.4255</v>
       </c>
       <c r="R6" t="n">
-        <v>20.6321</v>
+        <v>23.0125</v>
       </c>
       <c r="S6" t="n">
-        <v>15.2857</v>
+        <v>-4.8717</v>
       </c>
       <c r="T6" t="n">
-        <v>10.5273</v>
+        <v>-0.9793000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>4.7584</v>
+        <v>-3.8924</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8435000000000004</v>
+        <v>-6.1569</v>
       </c>
       <c r="W6" t="n">
-        <v>9.1008</v>
+        <v>9.684699999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.944099999999999</v>
+        <v>-15.8417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. MALARY</t>
+          <t>A. PIQUERAS CARBONELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03229999999999977</v>
+        <v>0.1782000000000004</v>
       </c>
       <c r="E7" t="n">
-        <v>24.0154</v>
+        <v>0.9913999999999998</v>
       </c>
       <c r="F7" t="n">
-        <v>-23.9832</v>
+        <v>-0.8133</v>
       </c>
       <c r="G7" t="n">
-        <v>10.1714</v>
+        <v>2.0635</v>
       </c>
       <c r="H7" t="n">
-        <v>9.264100000000001</v>
+        <v>-0.1415</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9074</v>
+        <v>2.2049</v>
       </c>
       <c r="J7" t="n">
-        <v>36.945</v>
+        <v>4.349</v>
       </c>
       <c r="K7" t="n">
-        <v>27.3719</v>
+        <v>2.047</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5732</v>
+        <v>2.302</v>
       </c>
       <c r="M7" t="n">
-        <v>-26.7736</v>
+        <v>-2.2853</v>
       </c>
       <c r="N7" t="n">
-        <v>-18.1077</v>
+        <v>-2.1884</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.666</v>
+        <v>-0.09709999999999996</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5871</v>
+        <v>-0.7934000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-21.4255</v>
+        <v>-5.1579</v>
       </c>
       <c r="R7" t="n">
-        <v>23.0125</v>
+        <v>4.3645</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.5694</v>
+        <v>-0.5597</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.189</v>
+        <v>-0.8783</v>
       </c>
       <c r="U7" t="n">
-        <v>-4.3804</v>
+        <v>0.3186</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.1569</v>
+        <v>-0.532</v>
       </c>
       <c r="W7" t="n">
-        <v>9.684699999999999</v>
+        <v>2.6789</v>
       </c>
       <c r="X7" t="n">
-        <v>-15.8417</v>
+        <v>-3.2109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PIQUERAS CARBONELL</t>
+          <t>D. TORRES PARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.157</v>
+        <v>-0.8097</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1331</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2902</v>
+        <v>-0.0048</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0635</v>
+        <v>-0.8097</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1415</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2049</v>
+        <v>-0.8097</v>
       </c>
       <c r="J8" t="n">
-        <v>4.349</v>
+        <v>-0.6802</v>
       </c>
       <c r="K8" t="n">
-        <v>2.047</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.302</v>
+        <v>-0.6802</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2853</v>
+        <v>-0.1295</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1884</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.09709999999999996</v>
+        <v>-0.1295</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7934000000000001</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.1579</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3645</v>
+        <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.895</v>
+        <v>-0.1984</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7365</v>
+        <v>-0.1247</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1584</v>
+        <v>-0.0737</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.2109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. TORRES PARRA</t>
+          <t>R. GUILLEN PILCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,61 +1108,61 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8097</v>
+        <v>-2.1702</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-2.7895</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0048</v>
+        <v>0.6193</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8097</v>
+        <v>-4.0421</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-2.7414</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8097</v>
+        <v>-1.3008</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6802</v>
+        <v>-2.5798</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-1.9398</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6802</v>
+        <v>-0.64</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1295</v>
+        <v>-1.4622</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.8016</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1295</v>
+        <v>-0.6607000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1984</v>
+        <v>0.08650000000000002</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1247</v>
+        <v>-0.2096</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0737</v>
+        <v>0.2962</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. GUILLEN PILCO</t>
+          <t>D. BOTUSAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5146</v>
+        <v>-2.2679</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9935</v>
+        <v>0.02549999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4791</v>
+        <v>-2.2934</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0421</v>
+        <v>-0.4158</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7414</v>
+        <v>-0.9223</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3008</v>
+        <v>0.5065999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5798</v>
+        <v>0.5072</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9398</v>
+        <v>-0.66</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.64</v>
+        <v>1.1672</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4622</v>
+        <v>-0.923</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8016</v>
+        <v>-0.2623</v>
       </c>
       <c r="O10" t="n">
         <v>-0.6607000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2578</v>
+        <v>-0.7765</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4137</v>
+        <v>-0.4817</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1558</v>
+        <v>-0.2948</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. BOTUSAN</t>
+          <t>J. BEJARANO MORENO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5842</v>
+        <v>-4.1948</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1786</v>
+        <v>-3.5753</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4056</v>
+        <v>-0.6194999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4158</v>
+        <v>0.5876999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9223</v>
+        <v>-0.3283</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5065999999999999</v>
+        <v>0.9161</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5072</v>
+        <v>1.8094</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.66</v>
+        <v>0.5242</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1672</v>
+        <v>1.2852</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.923</v>
+        <v>-1.2216</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2623</v>
+        <v>-0.8524999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6607000000000001</v>
+        <v>-0.3691</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3968</v>
+        <v>-3.1742</v>
       </c>
       <c r="Q11" t="n">
+        <v>-4.9596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-1.6084</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.425</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.1833</v>
+      </c>
+      <c r="V11" t="n">
         <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3968</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-1.0928</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.6858000000000001</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.407</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-1.4724</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BEJARANO MORENO</t>
+          <t>D. BUSTO VERANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6208</v>
+        <v>-6.3445</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0854</v>
+        <v>-6.06</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5352999999999999</v>
+        <v>-0.2845</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5876999999999999</v>
+        <v>-3.5354</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3283</v>
+        <v>1.1081</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9161</v>
+        <v>-4.6435</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8094</v>
+        <v>-1.7691</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5242</v>
+        <v>2.9394</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2852</v>
+        <v>-4.7084</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2216</v>
+        <v>-1.7663</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8524999999999999</v>
+        <v>-1.8313</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3691</v>
+        <v>0.065</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.1742</v>
+        <v>-0.3967000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.9596</v>
+        <v>-2.9757</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0343</v>
+        <v>-0.8685999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9352</v>
+        <v>-0.9065999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0991</v>
+        <v>0.03799999999999992</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.5437</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. BUSTO VERANO</t>
+          <t>P. GUASCH BENLLOCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.103299999999999</v>
+        <v>-6.5785</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.7347</v>
+        <v>-3.1973</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3686</v>
+        <v>-3.3811</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5354</v>
+        <v>-6.62</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1081</v>
+        <v>-5.9698</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.6435</v>
+        <v>-0.6502999999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7691</v>
+        <v>-0.3408</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9394</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.7084</v>
+        <v>0.3341</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7663</v>
+        <v>-6.279199999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8313</v>
+        <v>-5.295</v>
       </c>
       <c r="O13" t="n">
-        <v>0.065</v>
+        <v>-0.9843999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3967000000000001</v>
+        <v>5.753299999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9757</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>2.579</v>
+        <v>6.745299999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6273</v>
+        <v>-3.707</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5812</v>
+        <v>-1.8644</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04609999999999997</v>
+        <v>-1.8425</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5437</v>
+        <v>-2.0044</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1352</v>
+        <v>-2.0044</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.5213</v>
+        <v>-7.0023</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.1947</v>
+        <v>-1.9283</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.3264</v>
+        <v>-5.074</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6047</v>
@@ -1546,13 +1546,13 @@
         <v>3.3727</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.5668</v>
+        <v>-3.048</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3546</v>
+        <v>-1.0882</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2125</v>
+        <v>-1.96</v>
       </c>
       <c r="V14" t="n">
         <v>-2.3416</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GUASCH BENLLOCH</t>
+          <t>J. MESADO PLANELLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,61 +1576,61 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.879300000000001</v>
+        <v>-10.3571</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.2402</v>
+        <v>-5.6341</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.639399999999999</v>
+        <v>-4.723</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.62</v>
+        <v>-3.1323</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.9698</v>
+        <v>-2.4057</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6502999999999998</v>
+        <v>-0.7266</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3408</v>
+        <v>2.7713</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6749000000000001</v>
+        <v>1.1598</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3341</v>
+        <v>1.6116</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.279199999999999</v>
+        <v>-5.9037</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.295</v>
+        <v>-3.5655</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9843999999999999</v>
+        <v>-2.338</v>
       </c>
       <c r="P15" t="n">
-        <v>5.753299999999999</v>
+        <v>-1.7854</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-6.9433</v>
       </c>
       <c r="R15" t="n">
-        <v>6.745299999999999</v>
+        <v>5.158099999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.0082</v>
+        <v>-3.4351</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.9072</v>
+        <v>-1.462</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.1008</v>
+        <v>-1.9727</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0044</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MESADO PLANELLS</t>
+          <t>F. PASCUAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.6689</v>
+        <v>-11.6988</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.4732</v>
+        <v>-4.916399999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.1956</v>
+        <v>-6.782400000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.1323</v>
+        <v>-2.9043</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4057</v>
+        <v>-7.0008</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7266</v>
+        <v>4.0964</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7713</v>
+        <v>-0.6188</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1598</v>
+        <v>-3.1993</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6116</v>
+        <v>2.5807</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.9037</v>
+        <v>-2.2854</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.5655</v>
+        <v>-3.8014</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.338</v>
+        <v>1.5159</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7854</v>
+        <v>-2.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.9433</v>
+        <v>-5.1579</v>
       </c>
       <c r="R16" t="n">
-        <v>5.158099999999999</v>
+        <v>2.5791</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.7465</v>
+        <v>-1.7983</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.3011</v>
+        <v>-0.612</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.4456</v>
+        <v>-1.1862</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.0044</v>
+        <v>-4.4173</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.0044</v>
+        <v>-5.8898</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. PASCUAL</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.0186</v>
+        <v>-11.8811</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.5909</v>
+        <v>-5.7804</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.4277</v>
+        <v>-6.1007</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.9043</v>
+        <v>-13.6591</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.0008</v>
+        <v>-12.3269</v>
       </c>
       <c r="I17" t="n">
-        <v>4.0964</v>
+        <v>-1.3318</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6188</v>
+        <v>4.672800000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.1993</v>
+        <v>1.899</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5807</v>
+        <v>2.7737</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2854</v>
+        <v>-18.332</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.8014</v>
+        <v>-14.2261</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5159</v>
+        <v>-4.105799999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.579</v>
+        <v>-0.3967000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.1579</v>
+        <v>-21.0286</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5791</v>
+        <v>20.6321</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.118</v>
+        <v>3.0182</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2866</v>
+        <v>1.475</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.8315</v>
+        <v>1.5431</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.4173</v>
+        <v>-0.8435000000000004</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4724</v>
+        <v>9.1008</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.8898</v>
+        <v>-9.944099999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>M. MANYOSES ROCA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.2537</v>
+        <v>-14.031</v>
       </c>
       <c r="E18" t="n">
-        <v>5.363199999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-20.617</v>
+        <v>-5.530799999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.712399999999999</v>
+        <v>-7.1843</v>
       </c>
       <c r="H18" t="n">
-        <v>-16.5789</v>
+        <v>-8.486599999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>7.8662</v>
+        <v>1.3024</v>
       </c>
       <c r="J18" t="n">
-        <v>45.7692</v>
+        <v>-4.0898</v>
       </c>
       <c r="K18" t="n">
-        <v>26.1871</v>
+        <v>-3.6557</v>
       </c>
       <c r="L18" t="n">
-        <v>19.5818</v>
+        <v>-0.4342</v>
       </c>
       <c r="M18" t="n">
-        <v>-54.4816</v>
+        <v>-3.0945</v>
       </c>
       <c r="N18" t="n">
-        <v>-42.7661</v>
+        <v>-4.831</v>
       </c>
       <c r="O18" t="n">
-        <v>-11.7153</v>
+        <v>1.7364</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.380699999999999</v>
+        <v>3.9678</v>
       </c>
       <c r="Q18" t="n">
-        <v>-57.5314</v>
+        <v>-4.166</v>
       </c>
       <c r="R18" t="n">
-        <v>55.1508</v>
+        <v>8.133799999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.8044</v>
+        <v>-2.3168</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.4293</v>
+        <v>-0.7761</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.3754</v>
+        <v>-1.5408</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6437</v>
+        <v>-8.4976</v>
       </c>
       <c r="W18" t="n">
-        <v>21.5547</v>
+        <v>0.5319999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-18.911</v>
+        <v>-9.0296</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MANYOSES ROCA</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>-15.4204</v>
+        <v>-14.0987</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.2766</v>
+        <v>-4.6988</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.144</v>
+        <v>-9.399899999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.1843</v>
+        <v>9.650599999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.486599999999999</v>
+        <v>-11.1162</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3024</v>
+        <v>20.7669</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.0898</v>
+        <v>34.212</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.6557</v>
+        <v>14.0885</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4342</v>
+        <v>20.1236</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0945</v>
+        <v>-24.5615</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.831</v>
+        <v>-25.2046</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7364</v>
+        <v>0.6432</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9678</v>
+        <v>-18.053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.166</v>
+        <v>-55.9443</v>
       </c>
       <c r="R19" t="n">
-        <v>8.133799999999999</v>
+        <v>37.8912</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.7066</v>
+        <v>-10.2875</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5525</v>
+        <v>-5.3716</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1539</v>
+        <v>-4.916499999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-8.4976</v>
+        <v>4.591</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5319999999999999</v>
+        <v>22.4048</v>
       </c>
       <c r="X19" t="n">
-        <v>-9.0296</v>
+        <v>-17.8137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. CEBRIA PUCHADES</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-19.1616</v>
+        <v>-15.6577</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0745</v>
+        <v>4.869700000000003</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.0868</v>
+        <v>-20.5277</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.8485</v>
+        <v>-8.712399999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.3015</v>
+        <v>-16.5789</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4527</v>
+        <v>7.8662</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4484</v>
+        <v>45.7692</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5081000000000002</v>
+        <v>26.1871</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9402</v>
+        <v>19.5818</v>
       </c>
       <c r="M20" t="n">
-        <v>-11.2969</v>
+        <v>-54.4816</v>
       </c>
       <c r="N20" t="n">
-        <v>-11.8095</v>
+        <v>-42.7661</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5124999999999998</v>
+        <v>-11.7153</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3886</v>
+        <v>-2.380699999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-16.4658</v>
+        <v>-57.5314</v>
       </c>
       <c r="R20" t="n">
-        <v>15.0772</v>
+        <v>55.1508</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0472999999999999</v>
+        <v>-7.2086</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9938</v>
+        <v>-4.9227</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.0413</v>
+        <v>-2.286</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.8767</v>
+        <v>2.6437</v>
       </c>
       <c r="W20" t="n">
-        <v>4.949199999999999</v>
+        <v>21.5547</v>
       </c>
       <c r="X20" t="n">
-        <v>-14.8259</v>
+        <v>-18.911</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>J. ROSA DE SOUSA DA SILVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>-22.4164</v>
+        <v>-17.0307</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.347200000000001</v>
+        <v>-9.8005</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.0694</v>
+        <v>-7.230099999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>9.650599999999999</v>
+        <v>-9.475900000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.1162</v>
+        <v>-12.4341</v>
       </c>
       <c r="I21" t="n">
-        <v>20.7669</v>
+        <v>2.958</v>
       </c>
       <c r="J21" t="n">
-        <v>34.212</v>
+        <v>10.364</v>
       </c>
       <c r="K21" t="n">
-        <v>14.0885</v>
+        <v>4.641299999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>20.1236</v>
+        <v>5.7227</v>
       </c>
       <c r="M21" t="n">
-        <v>-24.5615</v>
+        <v>-19.8401</v>
       </c>
       <c r="N21" t="n">
-        <v>-25.2046</v>
+        <v>-17.0753</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6432</v>
+        <v>-2.7648</v>
       </c>
       <c r="P21" t="n">
-        <v>-18.053</v>
+        <v>3.769</v>
       </c>
       <c r="Q21" t="n">
-        <v>-55.9443</v>
+        <v>-22.0207</v>
       </c>
       <c r="R21" t="n">
-        <v>37.8912</v>
+        <v>25.7898</v>
       </c>
       <c r="S21" t="n">
-        <v>-18.6049</v>
+        <v>-5.8635</v>
       </c>
       <c r="T21" t="n">
-        <v>-10.0193</v>
+        <v>-4.442399999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-8.585900000000001</v>
+        <v>-1.4214</v>
       </c>
       <c r="V21" t="n">
-        <v>4.591</v>
+        <v>-5.4604</v>
       </c>
       <c r="W21" t="n">
-        <v>22.4048</v>
+        <v>6.298299999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-17.8137</v>
+        <v>-11.7587</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOUSA DA SILVA</t>
+          <t>V. CEBRIA PUCHADES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>-26.3961</v>
+        <v>-20.6784</v>
       </c>
       <c r="E22" t="n">
-        <v>-17.2601</v>
+        <v>-8.1694</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.135999999999999</v>
+        <v>-12.509</v>
       </c>
       <c r="G22" t="n">
-        <v>-9.475900000000001</v>
+        <v>-7.8485</v>
       </c>
       <c r="H22" t="n">
-        <v>-12.4341</v>
+        <v>-11.3015</v>
       </c>
       <c r="I22" t="n">
-        <v>2.958</v>
+        <v>3.4527</v>
       </c>
       <c r="J22" t="n">
-        <v>10.364</v>
+        <v>3.4484</v>
       </c>
       <c r="K22" t="n">
-        <v>4.641299999999999</v>
+        <v>0.5081000000000002</v>
       </c>
       <c r="L22" t="n">
-        <v>5.7227</v>
+        <v>2.9402</v>
       </c>
       <c r="M22" t="n">
-        <v>-19.8401</v>
+        <v>-11.2969</v>
       </c>
       <c r="N22" t="n">
-        <v>-17.0753</v>
+        <v>-11.8095</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.7648</v>
+        <v>0.5124999999999998</v>
       </c>
       <c r="P22" t="n">
-        <v>3.769</v>
+        <v>-1.3886</v>
       </c>
       <c r="Q22" t="n">
-        <v>-22.0207</v>
+        <v>-16.4658</v>
       </c>
       <c r="R22" t="n">
-        <v>25.7898</v>
+        <v>15.0772</v>
       </c>
       <c r="S22" t="n">
-        <v>-15.2292</v>
+        <v>-1.5643</v>
       </c>
       <c r="T22" t="n">
-        <v>-11.902</v>
+        <v>-0.1012000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.3273</v>
+        <v>-1.4634</v>
       </c>
       <c r="V22" t="n">
-        <v>-5.4604</v>
+        <v>-9.8767</v>
       </c>
       <c r="W22" t="n">
-        <v>6.298299999999999</v>
+        <v>4.949199999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-11.7587</v>
+        <v>-14.8259</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-32.1738</v>
+        <v>-21.5891</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.809</v>
+        <v>-4.573799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-21.3653</v>
+        <v>-17.0157</v>
       </c>
       <c r="G23" t="n">
         <v>-14.796</v>
@@ -2248,13 +2248,13 @@
         <v>38.4867</v>
       </c>
       <c r="S23" t="n">
-        <v>-18.9963</v>
+        <v>-8.4117</v>
       </c>
       <c r="T23" t="n">
-        <v>-12.3257</v>
+        <v>-6.091</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.6704</v>
+        <v>-2.3209</v>
       </c>
       <c r="V23" t="n">
         <v>6.1815</v>
@@ -2281,13 +2281,13 @@
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>-35.089</v>
+        <v>-29.3223</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.0684</v>
+        <v>-13.1243</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.0205</v>
+        <v>-16.1981</v>
       </c>
       <c r="G24" t="n">
         <v>-18.6804</v>
@@ -2326,13 +2326,13 @@
         <v>23.2112</v>
       </c>
       <c r="S24" t="n">
-        <v>-14.1215</v>
+        <v>-8.3545</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.6445</v>
+        <v>-3.7002</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.476800000000001</v>
+        <v>-4.6542</v>
       </c>
       <c r="V24" t="n">
         <v>-14.7853</v>
@@ -2359,16 +2359,16 @@
         <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>-114.8024</v>
+        <v>-95.70059999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>49.89609999999999</v>
+        <v>56.75440000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-164.6993</v>
+        <v>-152.4561</v>
       </c>
       <c r="G25" t="n">
-        <v>-11.9448</v>
+        <v>-11.94480000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-121.3221</v>
@@ -2392,7 +2392,7 @@
         <v>-264.1678</v>
       </c>
       <c r="O25" t="n">
-        <v>-56.8867</v>
+        <v>-56.88669999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-12.8939</v>
@@ -2401,19 +2401,19 @@
         <v>-371.9688</v>
       </c>
       <c r="R25" t="n">
-        <v>359.0763000000001</v>
+        <v>359.0763</v>
       </c>
       <c r="S25" t="n">
-        <v>-80.8283</v>
+        <v>-61.7264</v>
       </c>
       <c r="T25" t="n">
-        <v>-42.6033</v>
+        <v>-35.7456</v>
       </c>
       <c r="U25" t="n">
-        <v>-38.2257</v>
+        <v>-25.9822</v>
       </c>
       <c r="V25" t="n">
-        <v>-9.133700000000005</v>
+        <v>-9.133700000000001</v>
       </c>
       <c r="W25" t="n">
         <v>155.3612</v>
